--- a/branches/main/StructureDefinition-mii-pr-icu-muv-koerperlaenge.xlsx
+++ b/branches/main/StructureDefinition-mii-pr-icu-muv-koerperlaenge.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T11:25:36+00:00</t>
+    <t>2026-10-21T14:50:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -664,9 +664,6 @@
     <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
   </si>
   <si>
-    <t>closed</t>
-  </si>
-  <si>
     <t>CodeableConcept.coding</t>
   </si>
   <si>
@@ -762,6 +759,40 @@
   </si>
   <si>
     <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:loinc</t>
+  </si>
+  <si>
+    <t>loinc</t>
+  </si>
+  <si>
+    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="http://loinc.org"/&gt;
+  &lt;code value="8306-3"/&gt;
+  &lt;display value="Body height --lying"/&gt;
+&lt;/valueCoding&gt;</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:loinc.id</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:loinc.extension</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:loinc.system</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:loinc.version</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:loinc.code</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:loinc.display</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:loinc.userSelected</t>
   </si>
   <si>
     <t>Observation.code.coding:sct</t>
@@ -798,40 +829,6 @@
     <t>Observation.code.coding:sct.userSelected</t>
   </si>
   <si>
-    <t>Observation.code.coding:loinc</t>
-  </si>
-  <si>
-    <t>loinc</t>
-  </si>
-  <si>
-    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
-  &lt;system value="http://loinc.org"/&gt;
-  &lt;code value="8306-3"/&gt;
-  &lt;display value="Body height --lying"/&gt;
-&lt;/valueCoding&gt;</t>
-  </si>
-  <si>
-    <t>Observation.code.coding:loinc.id</t>
-  </si>
-  <si>
-    <t>Observation.code.coding:loinc.extension</t>
-  </si>
-  <si>
-    <t>Observation.code.coding:loinc.system</t>
-  </si>
-  <si>
-    <t>Observation.code.coding:loinc.version</t>
-  </si>
-  <si>
-    <t>Observation.code.coding:loinc.code</t>
-  </si>
-  <si>
-    <t>Observation.code.coding:loinc.display</t>
-  </si>
-  <si>
-    <t>Observation.code.coding:loinc.userSelected</t>
-  </si>
-  <si>
     <t>Observation.code.text</t>
   </si>
   <si>
@@ -933,6 +930,9 @@
   <si>
     <t xml:space="preserve">type:$this}
 </t>
+  </si>
+  <si>
+    <t>closed</t>
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
@@ -3678,7 +3678,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
         <v>180</v>
       </c>
@@ -3697,7 +3697,7 @@
         <v>82</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>75</v>
@@ -4068,10 +4068,10 @@
         <v>75</v>
       </c>
       <c r="AE20" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AF20" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="AF20" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>73</v>
@@ -4088,10 +4088,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4188,10 +4188,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4290,10 +4290,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4319,16 +4319,16 @@
         <v>97</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="N23" t="s" s="2">
+      <c r="O23" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>75</v>
@@ -4377,7 +4377,7 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>73</v>
@@ -4394,10 +4394,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4423,13 +4423,13 @@
         <v>190</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4479,7 +4479,7 @@
         <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>73</v>
@@ -4496,10 +4496,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4525,16 +4525,16 @@
         <v>103</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>75</v>
@@ -4583,7 +4583,7 @@
         <v>75</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>73</v>
@@ -4600,10 +4600,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4629,16 +4629,16 @@
         <v>190</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="O26" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>75</v>
@@ -4687,7 +4687,7 @@
         <v>75</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>73</v>
@@ -4704,10 +4704,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4730,19 +4730,19 @@
         <v>83</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>75</v>
@@ -4791,7 +4791,7 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>73</v>
@@ -4808,13 +4808,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>197</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>75</v>
@@ -4858,7 +4858,7 @@
         <v>75</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>75</v>
@@ -4897,7 +4897,7 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>73</v>
@@ -4914,10 +4914,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5014,10 +5014,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5116,10 +5116,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5145,16 +5145,16 @@
         <v>97</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="N31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>75</v>
@@ -5203,7 +5203,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>73</v>
@@ -5220,10 +5220,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5249,13 +5249,13 @@
         <v>190</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5305,7 +5305,7 @@
         <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>73</v>
@@ -5322,10 +5322,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5351,16 +5351,16 @@
         <v>103</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="N33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>75</v>
@@ -5409,7 +5409,7 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>73</v>
@@ -5426,10 +5426,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5455,16 +5455,16 @@
         <v>190</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="O34" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>75</v>
@@ -5513,7 +5513,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>73</v>
@@ -5530,10 +5530,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5556,19 +5556,19 @@
         <v>83</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="N35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>75</v>
@@ -5617,7 +5617,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>73</v>
@@ -5634,13 +5634,13 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>197</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>75</v>
@@ -5684,7 +5684,7 @@
         <v>75</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>75</v>
@@ -5723,7 +5723,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>73</v>
@@ -5740,10 +5740,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5840,10 +5840,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5942,10 +5942,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5971,16 +5971,16 @@
         <v>97</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>75</v>
@@ -6029,7 +6029,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>73</v>
@@ -6046,10 +6046,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6075,13 +6075,13 @@
         <v>190</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6131,7 +6131,7 @@
         <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>73</v>
@@ -6148,10 +6148,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6177,16 +6177,16 @@
         <v>103</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>75</v>
@@ -6235,7 +6235,7 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>73</v>
@@ -6252,10 +6252,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6281,16 +6281,16 @@
         <v>190</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="O42" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>75</v>
@@ -6339,7 +6339,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>73</v>
@@ -6356,10 +6356,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6382,19 +6382,19 @@
         <v>83</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="N43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>75</v>
@@ -6443,7 +6443,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>73</v>
@@ -6460,10 +6460,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6489,16 +6489,16 @@
         <v>190</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>75</v>
@@ -6547,7 +6547,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>73</v>
@@ -6564,10 +6564,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6590,19 +6590,19 @@
         <v>83</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="N45" t="s" s="2">
+      <c r="O45" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>75</v>
@@ -6651,7 +6651,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>73</v>
@@ -6668,10 +6668,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6694,16 +6694,16 @@
         <v>83</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6753,7 +6753,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>73</v>
@@ -6770,14 +6770,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -6796,19 +6796,19 @@
         <v>83</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="N47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>75</v>
@@ -6857,7 +6857,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>73</v>
@@ -6874,14 +6874,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -6900,19 +6900,19 @@
         <v>83</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="N48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>75</v>
@@ -6949,17 +6949,17 @@
         <v>75</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AC48" s="2"/>
       <c r="AD48" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>204</v>
+        <v>288</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>73</v>
@@ -6979,13 +6979,13 @@
         <v>290</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C49" t="s" s="2">
         <v>291</v>
       </c>
       <c r="D49" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7007,16 +7007,16 @@
         <v>292</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="N49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>75</v>
@@ -7065,7 +7065,7 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>73</v>
@@ -7085,13 +7085,13 @@
         <v>293</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C50" t="s" s="2">
         <v>294</v>
       </c>
       <c r="D50" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7113,16 +7113,16 @@
         <v>295</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>75</v>
@@ -7171,7 +7171,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>73</v>
@@ -7877,14 +7877,14 @@
         <v>75</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AC57" s="2"/>
       <c r="AD57" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>204</v>
+        <v>288</v>
       </c>
       <c r="AF57" t="s" s="2">
         <v>324</v>
@@ -8349,7 +8349,7 @@
         <v>350</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O62" t="s" s="2">
         <v>351</v>
@@ -8455,7 +8455,7 @@
         <v>359</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O63" t="s" s="2">
         <v>360</v>
@@ -10413,7 +10413,7 @@
         <v>474</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11273,7 +11273,7 @@
         <v>75</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AC90" s="2"/>
       <c r="AD90" t="s" s="2">
@@ -11747,7 +11747,7 @@
         <v>350</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O95" t="s" s="2">
         <v>351</v>
@@ -11853,7 +11853,7 @@
         <v>359</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O96" t="s" s="2">
         <v>360</v>

--- a/branches/main/StructureDefinition-mii-pr-icu-muv-koerperlaenge.xlsx
+++ b/branches/main/StructureDefinition-mii-pr-icu-muv-koerperlaenge.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.3</t>
+    <t>2027.0.0-ballot.3-rc.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T14:50:03+00:00</t>
+    <t>2026-10-30T08:50:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
